--- a/Assets/Resources/MasterData/CharacterData.xlsx
+++ b/Assets/Resources/MasterData/CharacterData.xlsx
@@ -8,24 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E8CDF86-A7A1-4B38-8110-7197D9EFFA2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5504A4E-1E98-4725-9651-1D585E1341C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45" yWindow="-15645" windowWidth="12465" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="900" yWindow="-15585" windowWidth="19680" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -60,6 +69,22 @@
   </si>
   <si>
     <t>rogue_sand_enemy2_</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>rogue_snow_enemy1_</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>rogue_urban_enemy2_</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>rogue_urban_enemy1_</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>actionID[]</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -124,10 +149,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -408,18 +434,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -438,19 +465,26 @@
       <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" s="1">
-        <v>0</v>
+        <f>A2+10000</f>
+        <v>10000</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="1">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="E2" s="1">
         <v>5</v>
@@ -458,13 +492,20 @@
       <c r="F2" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H2" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="1">
-        <v>1</v>
+        <f t="shared" ref="B3:B7" si="0">A3+10000</f>
+        <v>10001</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -478,13 +519,20 @@
       <c r="F3" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="1">
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>10002</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>8</v>
@@ -498,6 +546,96 @@
       <c r="F4" s="1">
         <v>2</v>
       </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1">
+        <f t="shared" si="0"/>
+        <v>10003</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1">
+        <v>11</v>
+      </c>
+      <c r="E5" s="1">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1">
+        <v>3</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1">
+        <f t="shared" si="0"/>
+        <v>10004</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="1">
+        <v>14</v>
+      </c>
+      <c r="E6" s="1">
+        <v>4</v>
+      </c>
+      <c r="F6" s="1">
+        <v>4</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1">
+        <f t="shared" si="0"/>
+        <v>10005</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="1">
+        <v>17</v>
+      </c>
+      <c r="E7" s="1">
+        <v>5</v>
+      </c>
+      <c r="F7" s="1">
+        <v>6</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="G8" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/Assets/Resources/MasterData/CharacterData.xlsx
+++ b/Assets/Resources/MasterData/CharacterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5504A4E-1E98-4725-9651-1D585E1341C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA780704-6DC0-4FC5-BF7D-9B5D46082FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="-15585" windowWidth="19680" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterData" sheetId="1" r:id="rId1"/>
@@ -487,7 +487,7 @@
         <v>100</v>
       </c>
       <c r="E2" s="1">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3" s="1">
         <v>-1</v>
@@ -550,7 +550,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:8">

--- a/Assets/Resources/MasterData/CharacterData.xlsx
+++ b/Assets/Resources/MasterData/CharacterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA780704-6DC0-4FC5-BF7D-9B5D46082FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B8B1D84-0BB5-47FC-9DEA-58BD19C55317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterData" sheetId="1" r:id="rId1"/>
@@ -520,7 +520,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H3" s="1">
         <v>-1</v>

--- a/Assets/Resources/MasterData/CharacterData.xlsx
+++ b/Assets/Resources/MasterData/CharacterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B8B1D84-0BB5-47FC-9DEA-58BD19C55317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5B11BA-74EE-4E47-98D1-A64A64988DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -487,7 +487,7 @@
         <v>100</v>
       </c>
       <c r="E2" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
